--- a/fa25repr1.xlsx
+++ b/fa25repr1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BB47682-30BF-4C03-A241-11142ED75127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2712D172-D049-43AF-88A7-F554002E5A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{0A538987-1B89-479E-9C18-3CDFD966561C}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{0A538987-1B89-479E-9C18-3CDFD966561C}"/>
   </bookViews>
   <sheets>
     <sheet name="fa25repr1" sheetId="1" r:id="rId1"/>
@@ -576,9 +576,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FE0DF2-EC66-4C85-A432-08726AF8AB5C}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,7 +607,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -623,8 +623,20 @@
       <c r="E2">
         <v>76</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>132</v>
+      </c>
+      <c r="G2">
+        <v>145</v>
+      </c>
+      <c r="H2">
+        <v>150</v>
+      </c>
+      <c r="I2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -643,8 +655,17 @@
       <c r="F3">
         <v>112</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>116</v>
+      </c>
+      <c r="H3">
+        <v>120</v>
+      </c>
+      <c r="I3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -673,7 +694,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -702,7 +723,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -731,7 +752,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -756,8 +777,11 @@
       <c r="H7">
         <v>94</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -782,8 +806,11 @@
       <c r="H8">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -805,8 +832,14 @@
       <c r="G9">
         <v>112</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -835,7 +868,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -860,8 +893,11 @@
       <c r="H11">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -890,7 +926,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -915,8 +951,11 @@
       <c r="H13">
         <v>106</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -941,8 +980,11 @@
       <c r="H14">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -971,7 +1013,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -1000,7 +1042,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -1025,8 +1067,11 @@
       <c r="H17">
         <v>114</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -1055,7 +1100,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -1084,7 +1129,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -1109,8 +1154,11 @@
       <c r="H20">
         <v>112</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I20">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -1139,7 +1187,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1168,7 +1216,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1197,7 +1245,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1226,7 +1274,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1255,7 +1303,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1284,7 +1332,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -1313,7 +1361,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1342,7 +1390,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1371,7 +1419,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -1400,7 +1448,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1429,7 +1477,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -1458,7 +1506,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1487,7 +1535,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -1516,7 +1564,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -1545,7 +1593,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1622,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -1603,7 +1651,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -1632,7 +1680,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -1661,7 +1709,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -1690,7 +1738,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -1719,7 +1767,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1748,7 +1796,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>24</v>
       </c>
